--- a/diseases/d091/1980-1984.xlsx
+++ b/diseases/d091/1980-1984.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5086,9 +5053,6 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="inlineStr">

--- a/diseases/d091/1980-1984.xlsx
+++ b/diseases/d091/1980-1984.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -751,19 +751,19 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1981-01-01</t>
+          <t>1980-01-01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1981-01</t>
+          <t>1980-01</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -772,12 +772,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -810,42 +810,42 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -907,38 +907,38 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1981-01-01</t>
+          <t>1980-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1981-01</t>
+          <t>1980-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Botulisme</t>
+          <t>Botulism</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -998,17 +998,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -1044,42 +1044,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1141,19 +1141,19 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1981-02-01</t>
+          <t>1981-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1981-02</t>
+          <t>1981-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AT4" t="n">
@@ -1200,42 +1200,42 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1981-02-01</t>
+          <t>1981-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1981-02</t>
+          <t>1981-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Botulisme</t>
+          <t>Botulism</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
         </is>
       </c>
       <c r="AT5" t="n">
@@ -1434,42 +1434,42 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1531,19 +1531,19 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1981-03-01</t>
+          <t>1981-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1981-03</t>
+          <t>1981-01</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1575,17 +1575,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1687,19 +1692,19 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1981-03-01</t>
+          <t>1981-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1981-03</t>
+          <t>1981-01</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1801,7 +1806,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1809,17 +1814,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1921,12 +1931,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1981-04-01</t>
+          <t>1981-02-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1981-04</t>
+          <t>1981-02</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1957,7 +1967,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1965,17 +1975,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2077,12 +2092,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1981-04-01</t>
+          <t>1981-02-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1981-04</t>
+          <t>1981-02</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2191,7 +2206,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2199,17 +2214,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2311,19 +2331,19 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1981-05-01</t>
+          <t>1981-03-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1981-05</t>
+          <t>1981-03</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2347,7 +2367,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2355,17 +2375,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2467,19 +2492,19 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1981-05-01</t>
+          <t>1981-03-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1981-05</t>
+          <t>1981-03</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2581,7 +2606,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2589,17 +2614,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2701,12 +2731,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1981-06-01</t>
+          <t>1981-04-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1981-06</t>
+          <t>1981-04</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2737,7 +2767,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2745,17 +2775,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2857,12 +2892,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1981-06-01</t>
+          <t>1981-04-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1981-06</t>
+          <t>1981-04</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2971,7 +3006,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2979,17 +3014,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -3091,12 +3131,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1981-07-01</t>
+          <t>1981-05-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1981-07</t>
+          <t>1981-05</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -3127,7 +3167,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -3135,17 +3175,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3247,12 +3292,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1981-07-01</t>
+          <t>1981-05-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1981-07</t>
+          <t>1981-05</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3361,7 +3406,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3369,17 +3414,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -3481,12 +3531,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1981-08-01</t>
+          <t>1981-06-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1981-08</t>
+          <t>1981-06</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3517,7 +3567,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -3525,17 +3575,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3637,12 +3692,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1981-08-01</t>
+          <t>1981-06-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1981-08</t>
+          <t>1981-06</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3751,7 +3806,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -3759,17 +3814,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -3871,12 +3931,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1981-09-01</t>
+          <t>1981-07-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1981-09</t>
+          <t>1981-07</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3907,7 +3967,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -3915,17 +3975,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -4027,12 +4092,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1981-09-01</t>
+          <t>1981-07-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1981-09</t>
+          <t>1981-07</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -4141,7 +4206,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -4149,17 +4214,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -4261,12 +4331,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1981-10-01</t>
+          <t>1981-08-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1981-10</t>
+          <t>1981-08</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -4297,7 +4367,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -4305,17 +4375,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -4417,12 +4492,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1981-10-01</t>
+          <t>1981-08-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1981-10</t>
+          <t>1981-08</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -4531,7 +4606,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -4539,17 +4614,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -4651,12 +4731,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1981-11-01</t>
+          <t>1981-09-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1981-11</t>
+          <t>1981-09</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -4687,7 +4767,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -4695,17 +4775,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -4807,12 +4892,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1981-11-01</t>
+          <t>1981-09-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1981-11</t>
+          <t>1981-09</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4921,7 +5006,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -4929,17 +5014,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -5041,12 +5131,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1981-12-01</t>
+          <t>1981-10-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1981-12</t>
+          <t>1981-10</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -5077,7 +5167,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
@@ -5085,17 +5175,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS24" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -5197,12 +5292,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1981-12-01</t>
+          <t>1981-10-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1981-12</t>
+          <t>1981-10</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -5311,65 +5406,2040 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1981-11-01</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1981-11</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1981-11-01</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1981-11</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Botulisme</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1981-12-01</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>1981-12</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1981-12-01</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>1981-12</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Botulisme</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1982-01-01</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>1982-01</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>6</v>
+      </c>
+      <c r="O30" t="n">
+        <v>6</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ25" t="inlineStr">
+      <c r="AQ30" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT25" t="n">
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
         <v>1</v>
       </c>
-      <c r="AU25" t="inlineStr">
+      <c r="AU30" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV25" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="BA25" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="BB25" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="BC25" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1982-01-01</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>1982-01</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>6</v>
+      </c>
+      <c r="O31" t="n">
+        <v>6</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1983-01-01</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>1983-01</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>7</v>
+      </c>
+      <c r="O32" t="n">
+        <v>7</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1983-01-01</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>1983-01</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>7</v>
+      </c>
+      <c r="O33" t="n">
+        <v>7</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1984-01-01</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>1984-01</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>9</v>
+      </c>
+      <c r="O34" t="n">
+        <v>9</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>1984-01-01</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>1984-01</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>9</v>
+      </c>
+      <c r="O35" t="n">
+        <v>9</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D13_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5406,7 +7476,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1981-12-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
     </row>
@@ -5418,7 +7488,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1981-01-01</t>
+          <t>1980-01-01</t>
         </is>
       </c>
     </row>
@@ -5489,7 +7559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -5499,7 +7569,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -5519,7 +7589,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -5529,7 +7599,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -5551,7 +7621,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
